--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7737,7 +7737,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>248</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -8455,7 +8455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>275</v>
       </c>
@@ -8474,7 +8474,7 @@
         <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -8577,7 +8577,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>285</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -8697,7 +8697,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>293</v>
       </c>
@@ -8716,7 +8716,7 @@
         <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -8817,7 +8817,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>302</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -10861,7 +10861,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>405</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
@@ -11579,7 +11579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>411</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>21</v>
@@ -11701,7 +11701,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>412</v>
       </c>
@@ -11720,7 +11720,7 @@
         <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
@@ -11821,7 +11821,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>413</v>
       </c>
@@ -11840,7 +11840,7 @@
         <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
@@ -11941,7 +11941,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>415</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
@@ -13985,7 +13985,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>438</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>90</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>21</v>
@@ -14703,7 +14703,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>444</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>21</v>
@@ -14825,7 +14825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>445</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>90</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>21</v>
@@ -14945,7 +14945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>446</v>
       </c>
@@ -14964,7 +14964,7 @@
         <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>21</v>
@@ -15065,7 +15065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>448</v>
       </c>
@@ -15084,7 +15084,7 @@
         <v>90</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9794" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9794" uniqueCount="1042">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2080,10 +2080,6 @@
   </si>
   <si>
     <t>Patient.deceased[x]</t>
-  </si>
-  <si>
-    <t>boolean
-dateTime</t>
   </si>
   <si>
     <t>Indicates if the individual is deceased or not</t>
@@ -9688,7 +9684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>314</v>
       </c>
@@ -9707,7 +9703,7 @@
         <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
@@ -12812,7 +12808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>460</v>
       </c>
@@ -12831,7 +12827,7 @@
         <v>82</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>21</v>
@@ -15936,7 +15932,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>493</v>
       </c>
@@ -15955,7 +15951,7 @@
         <v>82</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>21</v>
@@ -17518,7 +17514,7 @@
         <v>81</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>21</v>
@@ -20518,7 +20514,7 @@
         <v>81</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>21</v>
@@ -20530,19 +20526,19 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N142" t="s" s="2">
+      <c r="O142" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>21</v>
@@ -20579,14 +20575,14 @@
         <v>21</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AC142" s="2"/>
       <c r="AD142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AF142" t="s" s="2">
         <v>669</v>
@@ -20607,7 +20603,7 @@
         <v>21</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>108</v>
@@ -20616,7 +20612,7 @@
         <v>21</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AP142" t="s" s="2">
         <v>21</v>
@@ -20624,13 +20620,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>669</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>21</v>
@@ -20640,7 +20636,7 @@
         <v>81</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>21</v>
@@ -20655,16 +20651,16 @@
         <v>364</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>21</v>
@@ -20728,10 +20724,10 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>108</v>
@@ -20740,7 +20736,7 @@
         <v>21</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AP143" t="s" s="2">
         <v>21</v>
@@ -20748,13 +20744,13 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>669</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>21</v>
@@ -20764,7 +20760,7 @@
         <v>81</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>21</v>
@@ -20776,19 +20772,19 @@
         <v>91</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>21</v>
@@ -20852,10 +20848,10 @@
         <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>108</v>
@@ -20864,7 +20860,7 @@
         <v>21</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AP144" t="s" s="2">
         <v>21</v>
@@ -20872,10 +20868,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20901,16 +20897,16 @@
         <v>271</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="N145" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="N145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>21</v>
@@ -20959,7 +20955,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -20977,16 +20973,16 @@
         <v>21</v>
       </c>
       <c r="AL145" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AM145" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="AM145" t="s" s="2">
+      <c r="AN145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO145" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="AP145" t="s" s="2">
         <v>21</v>
@@ -20994,10 +20990,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21112,10 +21108,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21232,13 +21228,13 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="C148" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="C148" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="D148" t="s" s="2">
         <v>21</v>
@@ -21260,13 +21256,13 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -21352,10 +21348,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21381,16 +21377,16 @@
         <v>166</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>21</v>
@@ -21403,7 +21399,7 @@
         <v>21</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>21</v>
@@ -21418,28 +21414,28 @@
         <v>187</v>
       </c>
       <c r="Y149" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="Z149" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="Z149" t="s" s="2">
+      <c r="AA149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF149" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -21454,7 +21450,7 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>537</v>
@@ -21466,7 +21462,7 @@
         <v>21</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AP149" t="s" s="2">
         <v>21</v>
@@ -21474,10 +21470,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21503,13 +21499,13 @@
         <v>166</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -21523,7 +21519,7 @@
         <v>21</v>
       </c>
       <c r="T150" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="U150" t="s" s="2">
         <v>21</v>
@@ -21538,28 +21534,28 @@
         <v>187</v>
       </c>
       <c r="Y150" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="Z150" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="Z150" t="s" s="2">
+      <c r="AA150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF150" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -21586,7 +21582,7 @@
         <v>21</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AP150" t="s" s="2">
         <v>21</v>
@@ -21594,10 +21590,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21623,13 +21619,13 @@
         <v>104</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="O151" t="s" s="2">
         <v>543</v>
@@ -21645,43 +21641,43 @@
         <v>21</v>
       </c>
       <c r="T151" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF151" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -21696,7 +21692,7 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>545</v>
@@ -21708,7 +21704,7 @@
         <v>21</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>21</v>
@@ -21716,10 +21712,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21745,10 +21741,10 @@
         <v>104</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21763,43 +21759,43 @@
         <v>21</v>
       </c>
       <c r="T152" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF152" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -21814,19 +21810,19 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="AL152" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="AL152" t="s" s="2">
+      <c r="AM152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO152" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>21</v>
@@ -21834,10 +21830,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21952,10 +21948,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22068,13 +22064,13 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C155" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C155" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>21</v>
@@ -22096,13 +22092,13 @@
         <v>21</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="L155" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="M155" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -22171,7 +22167,7 @@
         <v>21</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>21</v>
@@ -22188,13 +22184,13 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C156" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C156" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>21</v>
@@ -22216,13 +22212,13 @@
         <v>21</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="M156" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -22291,7 +22287,7 @@
         <v>21</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>21</v>
@@ -22308,13 +22304,13 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C157" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C157" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="D157" t="s" s="2">
         <v>21</v>
@@ -22336,13 +22332,13 @@
         <v>21</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="L157" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="L157" t="s" s="2">
-        <v>754</v>
-      </c>
       <c r="M157" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -22411,7 +22407,7 @@
         <v>21</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>21</v>
@@ -22428,13 +22424,13 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C158" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C158" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>21</v>
@@ -22456,13 +22452,13 @@
         <v>21</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="L158" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="L158" t="s" s="2">
+      <c r="M158" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -22548,10 +22544,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22577,10 +22573,10 @@
         <v>104</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -22604,7 +22600,7 @@
         <v>21</v>
       </c>
       <c r="W159" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="X159" t="s" s="2">
         <v>21</v>
@@ -22666,14 +22662,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -22695,10 +22691,10 @@
         <v>104</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -22713,43 +22709,43 @@
         <v>21</v>
       </c>
       <c r="T160" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF160" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -22764,19 +22760,19 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AL160" t="s" s="2">
         <v>771</v>
       </c>
-      <c r="AL160" t="s" s="2">
+      <c r="AM160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO160" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="AP160" t="s" s="2">
         <v>21</v>
@@ -22784,14 +22780,14 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -22813,13 +22809,13 @@
         <v>104</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="N161" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -22833,43 +22829,43 @@
         <v>21</v>
       </c>
       <c r="T161" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF161" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -22887,16 +22883,16 @@
         <v>21</v>
       </c>
       <c r="AL161" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO161" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO161" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="AP161" t="s" s="2">
         <v>21</v>
@@ -22904,14 +22900,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -22933,10 +22929,10 @@
         <v>104</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>785</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>786</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22987,7 +22983,7 @@
         <v>21</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -23002,19 +22998,19 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AL162" t="s" s="2">
         <v>788</v>
       </c>
-      <c r="AL162" t="s" s="2">
+      <c r="AM162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO162" t="s" s="2">
         <v>789</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO162" t="s" s="2">
-        <v>790</v>
       </c>
       <c r="AP162" t="s" s="2">
         <v>21</v>
@@ -23022,14 +23018,14 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -23051,10 +23047,10 @@
         <v>104</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>793</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>794</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -23069,43 +23065,43 @@
         <v>21</v>
       </c>
       <c r="T163" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="U163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF163" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="U163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF163" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -23120,19 +23116,19 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="AL163" t="s" s="2">
         <v>797</v>
       </c>
-      <c r="AL163" t="s" s="2">
+      <c r="AM163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO163" t="s" s="2">
         <v>798</v>
-      </c>
-      <c r="AM163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO163" t="s" s="2">
-        <v>799</v>
       </c>
       <c r="AP163" t="s" s="2">
         <v>21</v>
@@ -23140,10 +23136,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23169,13 +23165,13 @@
         <v>104</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>801</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>803</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23225,7 +23221,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -23240,19 +23236,19 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="AL164" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="AL164" t="s" s="2">
+      <c r="AM164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO164" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="AM164" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN164" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO164" t="s" s="2">
-        <v>807</v>
       </c>
       <c r="AP164" t="s" s="2">
         <v>21</v>
@@ -23260,10 +23256,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23289,14 +23285,14 @@
         <v>249</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>809</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>810</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>21</v>
@@ -23309,43 +23305,43 @@
         <v>21</v>
       </c>
       <c r="T165" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF165" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="U165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF165" t="s" s="2">
-        <v>813</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -23372,7 +23368,7 @@
         <v>21</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AP165" t="s" s="2">
         <v>21</v>
@@ -23380,10 +23376,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23409,14 +23405,14 @@
         <v>235</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>21</v>
@@ -23444,11 +23440,11 @@
         <v>148</v>
       </c>
       <c r="Y166" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="Z166" t="s" s="2">
         <v>819</v>
       </c>
-      <c r="Z166" t="s" s="2">
-        <v>820</v>
-      </c>
       <c r="AA166" t="s" s="2">
         <v>21</v>
       </c>
@@ -23465,7 +23461,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -23483,16 +23479,16 @@
         <v>21</v>
       </c>
       <c r="AL166" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="AM166" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="AM166" t="s" s="2">
+      <c r="AN166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO166" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO166" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="AP166" t="s" s="2">
         <v>21</v>
@@ -23500,10 +23496,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23618,10 +23614,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23738,10 +23734,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23860,10 +23856,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23978,10 +23974,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24098,10 +24094,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24200,7 +24196,7 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>335</v>
@@ -24220,10 +24216,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24340,10 +24336,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -24440,7 +24436,7 @@
         <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>352</v>
@@ -24460,10 +24456,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24560,7 +24556,7 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>360</v>
@@ -24580,10 +24576,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24702,10 +24698,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24824,10 +24820,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24850,19 +24846,19 @@
         <v>21</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="L178" t="s" s="2">
         <v>839</v>
       </c>
-      <c r="L178" t="s" s="2">
+      <c r="M178" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>841</v>
       </c>
-      <c r="N178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>842</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>21</v>
@@ -24899,17 +24895,17 @@
         <v>21</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AC178" s="2"/>
       <c r="AD178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -24927,7 +24923,7 @@
         <v>21</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>108</v>
@@ -24936,7 +24932,7 @@
         <v>21</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP178" t="s" s="2">
         <v>21</v>
@@ -24944,13 +24940,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="C179" t="s" s="2">
         <v>846</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>847</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>21</v>
@@ -24975,16 +24971,16 @@
         <v>364</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="M179" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="M179" t="s" s="2">
+      <c r="N179" t="s" s="2">
         <v>841</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>842</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>21</v>
@@ -25033,7 +25029,7 @@
         <v>21</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -25051,7 +25047,7 @@
         <v>108</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>108</v>
@@ -25060,7 +25056,7 @@
         <v>21</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP179" t="s" s="2">
         <v>21</v>
@@ -25068,13 +25064,13 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="C180" t="s" s="2">
         <v>848</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="C180" t="s" s="2">
-        <v>849</v>
       </c>
       <c r="D180" t="s" s="2">
         <v>21</v>
@@ -25096,19 +25092,19 @@
         <v>21</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>841</v>
       </c>
-      <c r="N180" t="s" s="2">
+      <c r="O180" t="s" s="2">
         <v>842</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>21</v>
@@ -25157,7 +25153,7 @@
         <v>21</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -25175,7 +25171,7 @@
         <v>108</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>108</v>
@@ -25184,7 +25180,7 @@
         <v>21</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP180" t="s" s="2">
         <v>21</v>
@@ -25192,10 +25188,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25218,19 +25214,19 @@
         <v>21</v>
       </c>
       <c r="K181" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="L181" t="s" s="2">
         <v>852</v>
       </c>
-      <c r="L181" t="s" s="2">
+      <c r="M181" t="s" s="2">
         <v>853</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="N181" t="s" s="2">
         <v>854</v>
       </c>
-      <c r="N181" t="s" s="2">
+      <c r="O181" t="s" s="2">
         <v>855</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>856</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>21</v>
@@ -25279,7 +25275,7 @@
         <v>21</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -25297,7 +25293,7 @@
         <v>108</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>108</v>
@@ -25306,7 +25302,7 @@
         <v>21</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AP181" t="s" s="2">
         <v>21</v>
@@ -25314,10 +25310,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -25340,19 +25336,19 @@
         <v>21</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="L182" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="L182" t="s" s="2">
+      <c r="M182" t="s" s="2">
         <v>861</v>
       </c>
-      <c r="M182" t="s" s="2">
+      <c r="N182" t="s" s="2">
         <v>862</v>
       </c>
-      <c r="N182" t="s" s="2">
+      <c r="O182" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>21</v>
@@ -25401,7 +25397,7 @@
         <v>21</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -25413,13 +25409,13 @@
         <v>21</v>
       </c>
       <c r="AJ182" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="AK182" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL182" t="s" s="2">
         <v>865</v>
-      </c>
-      <c r="AK182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL182" t="s" s="2">
-        <v>866</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>108</v>
@@ -25436,10 +25432,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25554,10 +25550,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25674,14 +25670,14 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
@@ -25703,16 +25699,16 @@
         <v>111</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>870</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>871</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>872</v>
       </c>
       <c r="N185" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>21</v>
@@ -25761,7 +25757,7 @@
         <v>21</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -25796,10 +25792,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25825,14 +25821,14 @@
         <v>235</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>876</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>877</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>21</v>
@@ -25860,11 +25856,11 @@
         <v>148</v>
       </c>
       <c r="Y186" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="Z186" t="s" s="2">
         <v>879</v>
       </c>
-      <c r="Z186" t="s" s="2">
-        <v>880</v>
-      </c>
       <c r="AA186" t="s" s="2">
         <v>21</v>
       </c>
@@ -25881,7 +25877,7 @@
         <v>21</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -25908,7 +25904,7 @@
         <v>21</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="AP186" t="s" s="2">
         <v>21</v>
@@ -25916,10 +25912,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26034,10 +26030,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -26154,10 +26150,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26276,10 +26272,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -26394,10 +26390,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26514,10 +26510,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26616,7 +26612,7 @@
         <v>102</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="AL192" t="s" s="2">
         <v>335</v>
@@ -26636,10 +26632,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26756,10 +26752,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26856,7 +26852,7 @@
         <v>102</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>352</v>
@@ -26876,10 +26872,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26976,7 +26972,7 @@
         <v>102</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>360</v>
@@ -26996,10 +26992,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -27118,10 +27114,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -27240,10 +27236,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -27269,14 +27265,14 @@
         <v>519</v>
       </c>
       <c r="L198" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="M198" t="s" s="2">
         <v>897</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>898</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>21</v>
@@ -27325,7 +27321,7 @@
         <v>21</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
@@ -27352,7 +27348,7 @@
         <v>21</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AP198" t="s" s="2">
         <v>21</v>
@@ -27360,10 +27356,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -27478,10 +27474,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27598,10 +27594,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27720,10 +27716,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27842,10 +27838,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27942,7 +27938,7 @@
         <v>102</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>554</v>
@@ -27962,10 +27958,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -28062,7 +28058,7 @@
         <v>102</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>563</v>
@@ -28082,10 +28078,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -28200,10 +28196,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -28318,10 +28314,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28438,10 +28434,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -28467,13 +28463,13 @@
         <v>587</v>
       </c>
       <c r="L208" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="M208" t="s" s="2">
         <v>913</v>
       </c>
-      <c r="M208" t="s" s="2">
+      <c r="N208" t="s" s="2">
         <v>914</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>915</v>
       </c>
       <c r="O208" t="s" s="2">
         <v>591</v>
@@ -28525,7 +28521,7 @@
         <v>21</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -28552,7 +28548,7 @@
         <v>21</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="AP208" t="s" s="2">
         <v>21</v>
@@ -28560,10 +28556,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28678,10 +28674,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28798,10 +28794,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28896,7 +28892,7 @@
         <v>102</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AL211" t="s" s="2">
         <v>605</v>
@@ -28916,10 +28912,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -29018,7 +29014,7 @@
         <v>102</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="AL212" t="s" s="2">
         <v>613</v>
@@ -29038,10 +29034,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -29140,7 +29136,7 @@
         <v>102</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>537</v>
@@ -29160,10 +29156,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -29280,10 +29276,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -29398,10 +29394,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -29427,14 +29423,14 @@
         <v>271</v>
       </c>
       <c r="L216" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="M216" t="s" s="2">
         <v>928</v>
-      </c>
-      <c r="M216" t="s" s="2">
-        <v>929</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>21</v>
@@ -29483,7 +29479,7 @@
         <v>21</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -29501,7 +29497,7 @@
         <v>21</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AM216" t="s" s="2">
         <v>108</v>
@@ -29510,7 +29506,7 @@
         <v>21</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>21</v>
@@ -29518,10 +29514,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29636,10 +29632,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29756,13 +29752,13 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D219" t="s" s="2">
         <v>21</v>
@@ -29784,13 +29780,13 @@
         <v>21</v>
       </c>
       <c r="K219" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L219" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="L219" t="s" s="2">
+      <c r="M219" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="M219" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -29876,10 +29872,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29905,16 +29901,16 @@
         <v>166</v>
       </c>
       <c r="L220" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M220" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M220" t="s" s="2">
+      <c r="N220" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="N220" t="s" s="2">
+      <c r="O220" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="O220" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>21</v>
@@ -29927,7 +29923,7 @@
         <v>21</v>
       </c>
       <c r="T220" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="U220" t="s" s="2">
         <v>21</v>
@@ -29942,28 +29938,28 @@
         <v>187</v>
       </c>
       <c r="Y220" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="Z220" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="Z220" t="s" s="2">
+      <c r="AA220" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB220" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC220" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD220" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE220" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF220" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="AA220" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB220" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC220" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD220" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE220" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF220" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
@@ -29978,7 +29974,7 @@
         <v>102</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>537</v>
@@ -29990,7 +29986,7 @@
         <v>21</v>
       </c>
       <c r="AO220" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AP220" t="s" s="2">
         <v>21</v>
@@ -29998,10 +29994,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -30027,13 +30023,13 @@
         <v>166</v>
       </c>
       <c r="L221" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M221" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="M221" t="s" s="2">
+      <c r="N221" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
@@ -30047,7 +30043,7 @@
         <v>21</v>
       </c>
       <c r="T221" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="U221" t="s" s="2">
         <v>21</v>
@@ -30062,28 +30058,28 @@
         <v>187</v>
       </c>
       <c r="Y221" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="Z221" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="Z221" t="s" s="2">
+      <c r="AA221" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB221" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC221" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD221" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE221" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF221" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="AA221" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB221" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC221" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD221" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE221" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF221" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
@@ -30110,7 +30106,7 @@
         <v>21</v>
       </c>
       <c r="AO221" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AP221" t="s" s="2">
         <v>21</v>
@@ -30118,10 +30114,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -30147,13 +30143,13 @@
         <v>104</v>
       </c>
       <c r="L222" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M222" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="M222" t="s" s="2">
+      <c r="N222" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="N222" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="O222" t="s" s="2">
         <v>543</v>
@@ -30169,43 +30165,43 @@
         <v>21</v>
       </c>
       <c r="T222" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="U222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE222" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF222" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="U222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE222" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF222" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -30220,7 +30216,7 @@
         <v>102</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="AL222" t="s" s="2">
         <v>545</v>
@@ -30232,7 +30228,7 @@
         <v>21</v>
       </c>
       <c r="AO222" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AP222" t="s" s="2">
         <v>21</v>
@@ -30240,10 +30236,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -30269,10 +30265,10 @@
         <v>104</v>
       </c>
       <c r="L223" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M223" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="M223" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -30287,43 +30283,43 @@
         <v>21</v>
       </c>
       <c r="T223" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="U223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF223" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="U223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF223" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -30338,19 +30334,19 @@
         <v>102</v>
       </c>
       <c r="AK223" t="s" s="2">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AL223" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AM223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN223" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO223" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="AM223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN223" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO223" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="AP223" t="s" s="2">
         <v>21</v>
@@ -30358,10 +30354,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -30476,10 +30472,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30592,13 +30588,13 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D226" t="s" s="2">
         <v>21</v>
@@ -30620,13 +30616,13 @@
         <v>21</v>
       </c>
       <c r="K226" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="L226" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="L226" t="s" s="2">
+      <c r="M226" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="M226" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -30695,7 +30691,7 @@
         <v>21</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AM226" t="s" s="2">
         <v>21</v>
@@ -30712,13 +30708,13 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D227" t="s" s="2">
         <v>21</v>
@@ -30740,13 +30736,13 @@
         <v>21</v>
       </c>
       <c r="K227" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="L227" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="L227" t="s" s="2">
+      <c r="M227" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="M227" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
@@ -30815,7 +30811,7 @@
         <v>21</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>21</v>
@@ -30832,13 +30828,13 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D228" t="s" s="2">
         <v>21</v>
@@ -30860,13 +30856,13 @@
         <v>21</v>
       </c>
       <c r="K228" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="L228" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="L228" t="s" s="2">
-        <v>754</v>
-      </c>
       <c r="M228" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -30935,7 +30931,7 @@
         <v>21</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AM228" t="s" s="2">
         <v>21</v>
@@ -30952,13 +30948,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>21</v>
@@ -30980,13 +30976,13 @@
         <v>21</v>
       </c>
       <c r="K229" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="L229" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="L229" t="s" s="2">
+      <c r="M229" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -31072,10 +31068,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -31101,10 +31097,10 @@
         <v>104</v>
       </c>
       <c r="L230" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M230" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="M230" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -31128,7 +31124,7 @@
         <v>21</v>
       </c>
       <c r="W230" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="X230" t="s" s="2">
         <v>21</v>
@@ -31190,14 +31186,14 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
@@ -31219,10 +31215,10 @@
         <v>104</v>
       </c>
       <c r="L231" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="M231" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="M231" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -31237,43 +31233,43 @@
         <v>21</v>
       </c>
       <c r="T231" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="U231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF231" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="U231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF231" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -31288,19 +31284,19 @@
         <v>102</v>
       </c>
       <c r="AK231" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AL231" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AM231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN231" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO231" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="AM231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN231" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO231" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="AP231" t="s" s="2">
         <v>21</v>
@@ -31308,14 +31304,14 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
@@ -31337,13 +31333,13 @@
         <v>104</v>
       </c>
       <c r="L232" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M232" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="M232" t="s" s="2">
+      <c r="N232" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="N232" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -31357,43 +31353,43 @@
         <v>21</v>
       </c>
       <c r="T232" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="U232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF232" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="U232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF232" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -31411,16 +31407,16 @@
         <v>21</v>
       </c>
       <c r="AL232" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AM232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO232" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="AM232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN232" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO232" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="AP232" t="s" s="2">
         <v>21</v>
@@ -31428,14 +31424,14 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E233" s="2"/>
       <c r="F233" t="s" s="2">
@@ -31457,10 +31453,10 @@
         <v>104</v>
       </c>
       <c r="L233" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="M233" t="s" s="2">
         <v>785</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>786</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -31511,7 +31507,7 @@
         <v>21</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -31526,19 +31522,19 @@
         <v>102</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AL233" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AM233" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN233" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO233" t="s" s="2">
         <v>789</v>
-      </c>
-      <c r="AM233" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN233" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO233" t="s" s="2">
-        <v>790</v>
       </c>
       <c r="AP233" t="s" s="2">
         <v>21</v>
@@ -31546,14 +31542,14 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" t="s" s="2">
@@ -31575,10 +31571,10 @@
         <v>104</v>
       </c>
       <c r="L234" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="M234" t="s" s="2">
         <v>793</v>
-      </c>
-      <c r="M234" t="s" s="2">
-        <v>794</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -31593,43 +31589,43 @@
         <v>21</v>
       </c>
       <c r="T234" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="U234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF234" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="U234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF234" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
@@ -31644,19 +31640,19 @@
         <v>102</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AL234" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="AM234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO234" t="s" s="2">
         <v>798</v>
-      </c>
-      <c r="AM234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO234" t="s" s="2">
-        <v>799</v>
       </c>
       <c r="AP234" t="s" s="2">
         <v>21</v>
@@ -31664,10 +31660,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -31693,13 +31689,13 @@
         <v>104</v>
       </c>
       <c r="L235" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="M235" t="s" s="2">
         <v>801</v>
       </c>
-      <c r="M235" t="s" s="2">
+      <c r="N235" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="N235" t="s" s="2">
-        <v>803</v>
       </c>
       <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
@@ -31749,7 +31745,7 @@
         <v>21</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -31764,19 +31760,19 @@
         <v>102</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AL235" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="AM235" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN235" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO235" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="AM235" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN235" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO235" t="s" s="2">
-        <v>807</v>
       </c>
       <c r="AP235" t="s" s="2">
         <v>21</v>
@@ -31784,10 +31780,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -31813,14 +31809,14 @@
         <v>249</v>
       </c>
       <c r="L236" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="M236" t="s" s="2">
         <v>809</v>
-      </c>
-      <c r="M236" t="s" s="2">
-        <v>810</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>21</v>
@@ -31833,43 +31829,43 @@
         <v>21</v>
       </c>
       <c r="T236" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="U236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF236" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="U236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE236" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF236" t="s" s="2">
-        <v>813</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>81</v>
@@ -31896,7 +31892,7 @@
         <v>21</v>
       </c>
       <c r="AO236" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AP236" t="s" s="2">
         <v>21</v>
@@ -31904,10 +31900,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -31936,11 +31932,11 @@
         <v>636</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" t="s" s="2">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>21</v>
@@ -31989,7 +31985,7 @@
         <v>21</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
@@ -32016,7 +32012,7 @@
         <v>21</v>
       </c>
       <c r="AO237" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="AP237" t="s" s="2">
         <v>21</v>
@@ -32024,10 +32020,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -32142,10 +32138,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -32258,10 +32254,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C240" t="s" s="2">
         <v>651</v>
@@ -32378,10 +32374,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -32496,10 +32492,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -32525,14 +32521,14 @@
         <v>412</v>
       </c>
       <c r="L242" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="M242" t="s" s="2">
         <v>968</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>969</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>21</v>
@@ -32581,7 +32577,7 @@
         <v>21</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
@@ -32590,16 +32586,16 @@
         <v>90</v>
       </c>
       <c r="AI242" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AJ242" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK242" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="AL242" t="s" s="2">
         <v>972</v>
-      </c>
-      <c r="AL242" t="s" s="2">
-        <v>973</v>
       </c>
       <c r="AM242" t="s" s="2">
         <v>108</v>
@@ -32608,7 +32604,7 @@
         <v>21</v>
       </c>
       <c r="AO242" t="s" s="2">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="AP242" t="s" s="2">
         <v>21</v>
@@ -32616,10 +32612,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -32645,10 +32641,10 @@
         <v>249</v>
       </c>
       <c r="L243" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="M243" t="s" s="2">
         <v>976</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>977</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
@@ -32699,7 +32695,7 @@
         <v>21</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>81</v>
@@ -32717,7 +32713,7 @@
         <v>108</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="AM243" t="s" s="2">
         <v>108</v>
@@ -32734,10 +32730,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -32760,19 +32756,19 @@
         <v>21</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="L244" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="M244" t="s" s="2">
         <v>980</v>
       </c>
-      <c r="M244" t="s" s="2">
+      <c r="N244" t="s" s="2">
         <v>981</v>
       </c>
-      <c r="N244" t="s" s="2">
+      <c r="O244" t="s" s="2">
         <v>982</v>
-      </c>
-      <c r="O244" t="s" s="2">
-        <v>983</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>21</v>
@@ -32821,7 +32817,7 @@
         <v>21</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
@@ -32839,10 +32835,10 @@
         <v>21</v>
       </c>
       <c r="AL244" t="s" s="2">
+        <v>983</v>
+      </c>
+      <c r="AM244" t="s" s="2">
         <v>984</v>
-      </c>
-      <c r="AM244" t="s" s="2">
-        <v>985</v>
       </c>
       <c r="AN244" t="s" s="2">
         <v>21</v>
@@ -32856,10 +32852,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -32974,10 +32970,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -33094,14 +33090,14 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E247" s="2"/>
       <c r="F247" t="s" s="2">
@@ -33123,16 +33119,16 @@
         <v>111</v>
       </c>
       <c r="L247" t="s" s="2">
+        <v>870</v>
+      </c>
+      <c r="M247" t="s" s="2">
         <v>871</v>
-      </c>
-      <c r="M247" t="s" s="2">
-        <v>872</v>
       </c>
       <c r="N247" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O247" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>21</v>
@@ -33181,7 +33177,7 @@
         <v>21</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>81</v>
@@ -33216,10 +33212,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -33245,16 +33241,16 @@
         <v>235</v>
       </c>
       <c r="L248" t="s" s="2">
+        <v>989</v>
+      </c>
+      <c r="M248" t="s" s="2">
         <v>990</v>
       </c>
-      <c r="M248" t="s" s="2">
+      <c r="N248" t="s" s="2">
         <v>991</v>
       </c>
-      <c r="N248" t="s" s="2">
+      <c r="O248" t="s" s="2">
         <v>992</v>
-      </c>
-      <c r="O248" t="s" s="2">
-        <v>993</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>21</v>
@@ -33303,7 +33299,7 @@
         <v>21</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>90</v>
@@ -33318,19 +33314,19 @@
         <v>102</v>
       </c>
       <c r="AK248" t="s" s="2">
+        <v>993</v>
+      </c>
+      <c r="AL248" t="s" s="2">
         <v>994</v>
       </c>
-      <c r="AL248" t="s" s="2">
+      <c r="AM248" t="s" s="2">
         <v>995</v>
       </c>
-      <c r="AM248" t="s" s="2">
+      <c r="AN248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO248" t="s" s="2">
         <v>996</v>
-      </c>
-      <c r="AN248" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO248" t="s" s="2">
-        <v>997</v>
       </c>
       <c r="AP248" t="s" s="2">
         <v>21</v>
@@ -33338,10 +33334,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -33367,16 +33363,16 @@
         <v>364</v>
       </c>
       <c r="L249" t="s" s="2">
+        <v>998</v>
+      </c>
+      <c r="M249" t="s" s="2">
         <v>999</v>
       </c>
-      <c r="M249" t="s" s="2">
+      <c r="N249" t="s" s="2">
         <v>1000</v>
       </c>
-      <c r="N249" t="s" s="2">
+      <c r="O249" t="s" s="2">
         <v>1001</v>
-      </c>
-      <c r="O249" t="s" s="2">
-        <v>1002</v>
       </c>
       <c r="P249" t="s" s="2">
         <v>21</v>
@@ -33425,7 +33421,7 @@
         <v>21</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>81</v>
@@ -33440,19 +33436,19 @@
         <v>102</v>
       </c>
       <c r="AK249" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="AL249" t="s" s="2">
         <v>1003</v>
       </c>
-      <c r="AL249" t="s" s="2">
+      <c r="AM249" t="s" s="2">
         <v>1004</v>
       </c>
-      <c r="AM249" t="s" s="2">
+      <c r="AN249" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO249" t="s" s="2">
         <v>1005</v>
-      </c>
-      <c r="AN249" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO249" t="s" s="2">
-        <v>1006</v>
       </c>
       <c r="AP249" t="s" s="2">
         <v>21</v>
@@ -33460,14 +33456,14 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E250" s="2"/>
       <c r="F250" t="s" s="2">
@@ -33486,16 +33482,16 @@
         <v>21</v>
       </c>
       <c r="K250" t="s" s="2">
+        <v>1008</v>
+      </c>
+      <c r="L250" t="s" s="2">
         <v>1009</v>
       </c>
-      <c r="L250" t="s" s="2">
+      <c r="M250" t="s" s="2">
         <v>1010</v>
       </c>
-      <c r="M250" t="s" s="2">
+      <c r="N250" t="s" s="2">
         <v>1011</v>
-      </c>
-      <c r="N250" t="s" s="2">
-        <v>1012</v>
       </c>
       <c r="O250" s="2"/>
       <c r="P250" t="s" s="2">
@@ -33545,7 +33541,7 @@
         <v>21</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>81</v>
@@ -33560,10 +33556,10 @@
         <v>102</v>
       </c>
       <c r="AK250" t="s" s="2">
+        <v>1012</v>
+      </c>
+      <c r="AL250" t="s" s="2">
         <v>1013</v>
-      </c>
-      <c r="AL250" t="s" s="2">
-        <v>1014</v>
       </c>
       <c r="AM250" t="s" s="2">
         <v>108</v>
@@ -33572,7 +33568,7 @@
         <v>21</v>
       </c>
       <c r="AO250" t="s" s="2">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="AP250" t="s" s="2">
         <v>21</v>
@@ -33580,10 +33576,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -33609,16 +33605,16 @@
         <v>412</v>
       </c>
       <c r="L251" t="s" s="2">
+        <v>1016</v>
+      </c>
+      <c r="M251" t="s" s="2">
         <v>1017</v>
       </c>
-      <c r="M251" t="s" s="2">
+      <c r="N251" t="s" s="2">
         <v>1018</v>
       </c>
-      <c r="N251" t="s" s="2">
+      <c r="O251" t="s" s="2">
         <v>1019</v>
-      </c>
-      <c r="O251" t="s" s="2">
-        <v>1020</v>
       </c>
       <c r="P251" t="s" s="2">
         <v>21</v>
@@ -33667,7 +33663,7 @@
         <v>21</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>81</v>
@@ -33682,13 +33678,13 @@
         <v>102</v>
       </c>
       <c r="AK251" t="s" s="2">
+        <v>1020</v>
+      </c>
+      <c r="AL251" t="s" s="2">
+        <v>972</v>
+      </c>
+      <c r="AM251" t="s" s="2">
         <v>1021</v>
-      </c>
-      <c r="AL251" t="s" s="2">
-        <v>973</v>
-      </c>
-      <c r="AM251" t="s" s="2">
-        <v>1022</v>
       </c>
       <c r="AN251" t="s" s="2">
         <v>21</v>
@@ -33702,10 +33698,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -33716,7 +33712,7 @@
         <v>81</v>
       </c>
       <c r="G252" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H252" t="s" s="2">
         <v>21</v>
@@ -33728,19 +33724,19 @@
         <v>91</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="L252" t="s" s="2">
+        <v>1023</v>
+      </c>
+      <c r="M252" t="s" s="2">
         <v>1024</v>
       </c>
-      <c r="M252" t="s" s="2">
+      <c r="N252" t="s" s="2">
         <v>1025</v>
       </c>
-      <c r="N252" t="s" s="2">
+      <c r="O252" t="s" s="2">
         <v>1026</v>
-      </c>
-      <c r="O252" t="s" s="2">
-        <v>1027</v>
       </c>
       <c r="P252" t="s" s="2">
         <v>21</v>
@@ -33789,7 +33785,7 @@
         <v>21</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>81</v>
@@ -33807,7 +33803,7 @@
         <v>21</v>
       </c>
       <c r="AL252" t="s" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AM252" t="s" s="2">
         <v>108</v>
@@ -33824,10 +33820,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -33942,10 +33938,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -34062,14 +34058,14 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E255" s="2"/>
       <c r="F255" t="s" s="2">
@@ -34091,16 +34087,16 @@
         <v>111</v>
       </c>
       <c r="L255" t="s" s="2">
+        <v>870</v>
+      </c>
+      <c r="M255" t="s" s="2">
         <v>871</v>
-      </c>
-      <c r="M255" t="s" s="2">
-        <v>872</v>
       </c>
       <c r="N255" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O255" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="P255" t="s" s="2">
         <v>21</v>
@@ -34149,7 +34145,7 @@
         <v>21</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>81</v>
@@ -34184,10 +34180,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -34210,16 +34206,16 @@
         <v>91</v>
       </c>
       <c r="K256" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="L256" t="s" s="2">
         <v>1033</v>
       </c>
-      <c r="L256" t="s" s="2">
+      <c r="M256" t="s" s="2">
         <v>1034</v>
       </c>
-      <c r="M256" t="s" s="2">
+      <c r="N256" t="s" s="2">
         <v>1035</v>
-      </c>
-      <c r="N256" t="s" s="2">
-        <v>1036</v>
       </c>
       <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
@@ -34269,7 +34265,7 @@
         <v>21</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>90</v>
@@ -34296,7 +34292,7 @@
         <v>21</v>
       </c>
       <c r="AO256" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="AP256" t="s" s="2">
         <v>21</v>
@@ -34304,10 +34300,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -34333,10 +34329,10 @@
         <v>166</v>
       </c>
       <c r="L257" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="M257" t="s" s="2">
         <v>1039</v>
-      </c>
-      <c r="M257" t="s" s="2">
-        <v>1040</v>
       </c>
       <c r="N257" s="2"/>
       <c r="O257" s="2"/>
@@ -34366,11 +34362,11 @@
         <v>187</v>
       </c>
       <c r="Y257" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="Z257" t="s" s="2">
         <v>1040</v>
       </c>
-      <c r="Z257" t="s" s="2">
-        <v>1041</v>
-      </c>
       <c r="AA257" t="s" s="2">
         <v>21</v>
       </c>
@@ -34387,7 +34383,7 @@
         <v>21</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>90</v>
@@ -34405,7 +34401,7 @@
         <v>108</v>
       </c>
       <c r="AL257" t="s" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="AM257" t="s" s="2">
         <v>108</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -932,7 +932,7 @@
     <t>Patient.identifier.use</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
     <t>The purpose of this identifier.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
